--- a/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Martin Pio Concha - jr. Independencia - jr. Dos de Mayo- Av. General Gamarra</t>
+          <t>Jirón Martin Pio Concha / Jirón Independencia</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-12363</t>
+          <t>I-12366</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.863317</t>
+          <t>-12.8609029</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-72.695206</t>
+          <t>-72.6939806</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>I.E. N° 50226 - La Inmaculada</t>
+          <t>Jirón Espinar / Jirón Quillabamba</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-14599</t>
+          <t>I-14599</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>JR. GENERAL GAMARRA</t>
+          <t>Avenida Francisco Bolognesi / Calle Alameda</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,12 +639,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-12366</t>
+          <t>I-266558</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>080901</t>
+          <t>080902</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -659,27 +659,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SANTA ANA</t>
+          <t>ECHARATE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.8609029</t>
+          <t>-12.7641185</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-72.6939806</t>
+          <t>-72.5824211</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jr. Espinar / Jr. Quillabamba</t>
+          <t>Jirón Alameda Arusayhua / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-50368</t>
+          <t>I-33726</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.8709578</t>
+          <t>-12.857118</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-72.7016178</t>
+          <t>-72.692696</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Nicanor Larrea</t>
+          <t>Jirón General Gamarra / Jirón Pangoa</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-606275</t>
+          <t>I-50368</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.8707794</t>
+          <t>-12.8709578</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-72.7018914</t>
+          <t>-72.7016178</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Nicanor Larrea / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-33726</t>
+          <t>I-50313</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.857118</t>
+          <t>-12.871719</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-72.692696</t>
+          <t>-72.69413</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>I.E  la Convencion</t>
+          <t>Jirón 4 de Noviembre / Jirón 25 de Julio</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-50313</t>
+          <t>I-12363</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.871719</t>
+          <t>-12.863317</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-72.69413</t>
+          <t>-72.695206</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>JR. VILCABAMBA con JR. 04 DE NOVIEMBRE</t>
+          <t>I.E. N° 50226 / La Inmaculada</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -891,6 +891,422 @@
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-389859</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-12.616977</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-72.4392236</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-617526</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>080902</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ECHARATE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-12.4885291</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-72.9985545</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-352953</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-12.4347303</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-72.3977949</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-352961</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-12.4506322</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-72.341677</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-352955</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-12.4443919</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-72.3521655</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-352957</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-12.4400949</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-72.3677891</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-352959</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-12.4331518</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-72.3763548</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-12342</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SANTA ANA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-12.861711</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-72.69274</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Jirón Dos de Mayo / Jirón Martin Pio Concha</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>080901</t>
         </is>

--- a/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,162 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-211142</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-12.6407985</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-72.6434852</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-352941</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-12.4356298</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-72.3970239</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-352942</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-12.4282943</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-72.3907828</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jirón Martin Pio Concha / Jirón Independencia</t>
+          <t>Jirón Independencia / Jirón Martin Pio Concha</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Francisco Bolognesi / Calle Alameda</t>
+          <t>Avenida Francisco Bolognesi / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jirón 4 de Noviembre / Jirón 25 de Julio</t>
+          <t>Jirón 25 de Julio / Jirón 4 de Noviembre / Jirón Alborada</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>I.E. N° 50226 / La Inmaculada</t>
+          <t>Jirón Independencia / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1463,6 +1463,214 @@
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-211147</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-12.647802</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-72.5986917</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-352933</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-12.4375937</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-72.381217</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-378491</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-12.6364916</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-72.6102045</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>080901</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-378490</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>080906</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LA CONVENCION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>QUELLOUNO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-12.5757886</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-72.610432</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>080901</t>
         </is>

--- a/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-12344</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>080901</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SANTA ANA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-12.8627113</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-12366</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>080901</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SANTA ANA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-12.8609029</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-14599</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>080901</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SANTA ANA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-12.8574009</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-266558</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>080902</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ECHARATE</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-12.7641185</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-33726</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>080901</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SANTA ANA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-12.857118</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-50368</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>080901</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SANTA ANA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-12.8709578</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-50313</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>080901</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SANTA ANA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-12.871719</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-12363</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>080901</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SANTA ANA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-12.863317</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-389859</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-12.616977</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-617526</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>080902</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ECHARATE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-12.4885291</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-352953</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-12.4347303</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-352961</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-12.4506322</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-352955</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-12.4443919</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-352957</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-12.4400949</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-352959</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-12.4331518</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-12342</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>080901</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>SANTA ANA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-12.861711</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-211142</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-12.6407985</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-352941</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-12.4356298</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-352942</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-12.4282943</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-211147</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-12.647802</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-352933</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-12.4375937</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-378491</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-12.6364916</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>080901</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LA_CONVENCION</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SANTA_ANA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-378490</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>080906</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>LA CONVENCION</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>QUELLOUNO</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-12.5757886</t>
@@ -1668,11 +1553,6 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>080901</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -535,12 +535,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -582,12 +582,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -629,12 +629,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1475,12 +1475,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">

--- a/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -585,17 +585,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.8574009</t>
+          <t>-12.862107</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-72.6959152</t>
+          <t>-72.694825</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Francisco Bolognesi / Calle s / n</t>
+          <t>Av. Francisco Bolognesi n/ Jr. Dos de Mayo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.857118</t>
+          <t>-12.856654</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-72.692696</t>
+          <t>-72.693408</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jirón General Gamarra / Jirón Pangoa</t>
+          <t>Av. General Gamarra / Jr. Kumpirushiato</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -773,17 +773,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.871719</t>
+          <t>-12.859019</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-72.69413</t>
+          <t>-72.694449</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jirón 25 de Julio / Jirón 4 de Noviembre / Jirón Alborada</t>
+          <t>Jr. Espinar / Jr. Cirialo</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.863317</t>
+          <t>-12.869919</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-72.695206</t>
+          <t>-72.696844</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jirón Independencia / Calle s / n</t>
+          <t>Jr. Alejandro Valdivia / Av. Francisca Zubiaga</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1196,17 +1196,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12.861711</t>
+          <t>-12.859716</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-72.69274</t>
+          <t>-72.693181</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Jirón Dos de Mayo / Jirón Martin Pio Concha</t>
+          <t>Jr. Sabas Sarazola / Jr. Martin Pio Concha</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">

--- a/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/Intersecciones/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-12344</t>
+          <t>I-617526</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.8627113</t>
+          <t>-12.4885291</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-72.69256569</t>
+          <t>-72.9985545</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jirón Independencia / Jirón Martin Pio Concha</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-12366</t>
+          <t>I-50368</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.8609029</t>
+          <t>-12.8709578</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-72.6939806</t>
+          <t>-72.7016178</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jirón Espinar / Jirón Quillabamba</t>
+          <t>Avenida Nicanor Larrea / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-14599</t>
+          <t>I-50313</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.862107</t>
+          <t>-12.859019</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-72.694825</t>
+          <t>-72.694449</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Av. Francisco Bolognesi n/ Jr. Dos de Mayo</t>
+          <t>Jr. Espinar / Jr. Cirialo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-266558</t>
+          <t>I-389859</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.7641185</t>
+          <t>-12.616977</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-72.5824211</t>
+          <t>-72.4392236</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jirón Alameda Arusayhua / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-33726</t>
+          <t>I-378491</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.856654</t>
+          <t>-12.6364916</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-72.693408</t>
+          <t>-72.6102045</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Av. General Gamarra / Jr. Kumpirushiato</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,27 +721,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-50368</t>
+          <t>I-378490</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.8709578</t>
+          <t>-12.5757886</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-72.7016178</t>
+          <t>-72.610432</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Nicanor Larrea / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-50313</t>
+          <t>I-352961</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.859019</t>
+          <t>-12.4506322</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-72.694449</t>
+          <t>-72.341677</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jr. Espinar / Jr. Cirialo</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-12363</t>
+          <t>I-352959</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.869919</t>
+          <t>-12.4331518</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-72.696844</t>
+          <t>-72.3763548</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jr. Alejandro Valdivia / Av. Francisca Zubiaga</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-389859</t>
+          <t>I-352957</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.616977</t>
+          <t>-12.4400949</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-72.4392236</t>
+          <t>-72.3677891</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-617526</t>
+          <t>I-352955</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-12.4885291</t>
+          <t>-12.4443919</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-72.9985545</t>
+          <t>-72.3521655</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-352961</t>
+          <t>I-352942</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-12.4506322</t>
+          <t>-12.4282943</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-72.341677</t>
+          <t>-72.3907828</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-352955</t>
+          <t>I-352941</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-12.4443919</t>
+          <t>-12.4356298</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-72.3521655</t>
+          <t>-72.3970239</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-352957</t>
+          <t>I-352933</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-12.4400949</t>
+          <t>-12.4375937</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-72.3677891</t>
+          <t>-72.381217</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-352959</t>
+          <t>I-33726</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-12.4331518</t>
+          <t>-12.856654</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-72.3763548</t>
+          <t>-72.693408</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Av. General Gamarra / Jr. Kumpirushiato</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-12342</t>
+          <t>I-266558</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12.859716</t>
+          <t>-12.7641185</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-72.693181</t>
+          <t>-72.5824211</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Jr. Sabas Sarazola / Jr. Martin Pio Concha</t>
+          <t>Jirón Alameda Arusayhua / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-211142</t>
+          <t>I-211147</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-12.6407985</t>
+          <t>-12.647802</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-72.6434852</t>
+          <t>-72.5986917</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-352941</t>
+          <t>I-211142</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-12.4356298</t>
+          <t>-12.6407985</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-72.3970239</t>
+          <t>-72.6434852</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1332,22 +1332,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-352942</t>
+          <t>I-14599</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-12.4282943</t>
+          <t>-12.862107</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-72.3907828</t>
+          <t>-72.694825</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Av. Francisco Bolognesi n/ Jr. Dos de Mayo</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1379,27 +1379,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-211147</t>
+          <t>I-12366</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-12.647802</t>
+          <t>-12.8609029</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-72.5986917</t>
+          <t>-72.6939806</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón Espinar / Jirón Quillabamba</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1426,22 +1426,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-352933</t>
+          <t>I-12363</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-12.4375937</t>
+          <t>-12.869919</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-72.381217</t>
+          <t>-72.696844</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jr. Alejandro Valdivia / Av. Francisca Zubiaga</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-378491</t>
+          <t>I-12344</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-12.6364916</t>
+          <t>-12.8627113</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-72.6102045</t>
+          <t>-72.69256569</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón Martin Pio Concha / Jirón Independencia</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-378490</t>
+          <t>I-12342</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-12.5757886</t>
+          <t>-12.859716</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-72.610432</t>
+          <t>-72.693181</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jr. Sabas Sarazola / Jr. Martin Pio Concha</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
